--- a/tasks/finalpool/12306-wc-supplier-visit-excel-email-gcal/groundtruth_workspace/Supplier_Visit_Plan.xlsx
+++ b/tasks/finalpool/12306-wc-supplier-visit-excel-email-gcal/groundtruth_workspace/Supplier_Visit_Plan.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Monthly_Sales</t>
+          <t>Total_Sales</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -466,23 +466,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30kg Digital Scale</t>
+          <t>30kg digital scale for shop and kitchen green display 72hrs battery backup weight machine</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SCALE-30KG-1071</t>
+          <t>30KG-DIGITAL-SCALE-1071</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>TechWorld Electronics</t>
+          <t>Asia Tech Trading</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -502,23 +502,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Infinity JBL Wireless Headphone</t>
+          <t>Infinity (JBL Glide 500, 20 Hrs Playtime with Quick Charge, Wireless On Ear Headphone with Mic, Deep Bass, Dual Equalizer,...</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>INF-JBL-GLIDE-1020</t>
+          <t>INFINITY-JBL-GLIDE-1020</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>38</v>
+        <v>124</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SmartGadgets Co</t>
+          <t>Asia Tech Trading</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -534,32 +534,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CASEOLOGY Samsung Galaxy Case</t>
+          <t>Silencer Panels, Flame Retardant Sound‑Absorption, Polyester Fiber Stable for Recording Studio Home Theater Black</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CASE-S23U-1022</t>
+          <t>SILENCER-PANELS-FLAM-1079</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>32</v>
+        <v>156</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Digital Supplies Ltd</t>
+          <t>Asia Tech Trading</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Guangzhou</t>
+          <t>Shanghai</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -570,27 +570,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Eloies Tripod for Mobile</t>
+          <t>TYPE-C Earphone for OnePlus 8 Pro , OnePlus Eight Pro in Ear Type C Wired Earphones with Mic, Braided 1.2 Metre Cable, Met...</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TRIPOD-JAGUAR-1031</t>
+          <t>TYPEC-EARPHONE-FOR-1045</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>28</v>
+        <v>139</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mobile Tech Inc</t>
+          <t>Digital Dreams Supply</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -606,37 +606,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FOLX Milanese Mesh Watch Band</t>
+          <t>BOXTUDIO®- LIGHTBOX- Tabletop Portable PhotoStudio(40x40x40cms)- Product Photography Light Tent- Think Inside The Box !-10...</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FOLX-FMS1210-1003</t>
+          <t>BOXTUDIO-LIGHTBOX-TA-1039</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>22</v>
+        <v>183</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ComputerWorld</t>
+          <t>SmartHome Wholesale</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Shanghai</t>
+          <t>Guangzhou</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -699,21 +699,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>G11</t>
+          <t>G1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>331</v>
+        <v>268</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TechWorld Electronics</t>
+          <t>Asia Tech Trading</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SmartGadgets Co</t>
+          <t>Asia Tech Trading</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Stock replenishment - JBL Headphones</t>
+          <t>Stock replenishment - Wireless Headphones</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ComputerWorld</t>
+          <t>Asia Tech Trading</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -885,12 +885,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Supply agreement - Watch Bands</t>
+          <t>Stock replenishment - Studio Equipment</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Digital Supplies Ltd</t>
+          <t>Digital Dreams Supply</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stock replenishment - Phone Cases</t>
+          <t>Stock replenishment - Earphones</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mobile Tech Inc</t>
+          <t>SmartHome Wholesale</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stock replenishment - Tripods</t>
+          <t>Stock replenishment - Photo Equipment</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
